--- a/website/static/playground-samples/sample-template.xlsx
+++ b/website/static/playground-samples/sample-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Renewal Report" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
@@ -41,13 +41,16 @@
     <t>Customer Renewal Pipeline</t>
   </si>
   <si>
-    <t>Operators upload raw.xlsx and this template. Rules are archived in _config.</t>
+    <t>Operators upload raw.xlsx and this template. Rules are archived in __config__.</t>
   </si>
   <si>
     <t>Accounts</t>
   </si>
   <si>
     <t>{{ COUNT() }}</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Priority rule</t>
@@ -90,7 +93,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -100,41 +103,25 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF185C37"/>
-      <sz val="20"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF68716D"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF185C37"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF666666"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F3EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF217846"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -142,46 +129,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFC8D0CA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFC8D0CA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9E2DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,12 +490,12 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -538,7 +503,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -546,7 +511,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -554,7 +519,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
@@ -572,76 +537,79 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="E6" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" t="s">
         <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
